--- a/technician_forms/007_street_light_maintenance_checklist_form--technician_forms.xlsx
+++ b/technician_forms/007_street_light_maintenance_checklist_form--technician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'general',_'value':_'general'}</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'General', 'value': 'General'}</t>
+          <t>General</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'technician',_'value':_'technician'}</t>
+          <t>technician</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Technician', 'value': 'Technician'}</t>
+          <t>Technician</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'supervisor',_'value':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Supervisor', 'value': 'Supervisor'}</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'electric',_'value':_'electric'}</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Electric', 'value': 'Electric'}</t>
+          <t>Electric</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'solar',_'value':_'solar'}</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Solar', 'value': 'Solar'}</t>
+          <t>Solar</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'gas',_'value':_'gas'}</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Gas', 'value': 'Gas'}</t>
+          <t>Gas</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'electric',_'value':_'electric'}</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Electric', 'value': 'Electric'}</t>
+          <t>Electric</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'gas',_'value':_'gas'}</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Gas', 'value': 'Gas'}</t>
+          <t>Gas</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'water',_'value':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Water', 'value': 'Water'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'concrete',_'value':_'concrete'}</t>
+          <t>concrete</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Concrete', 'value': 'Concrete'}</t>
+          <t>Concrete</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'steel',_'value':_'steel'}</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Steel', 'value': 'Steel'}</t>
+          <t>Steel</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'wood',_'value':_'wood'}</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Wood', 'value': 'Wood'}</t>
+          <t>Wood</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'steel',_'value':_'steel'}</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Steel', 'value': 'Steel'}</t>
+          <t>Steel</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'aluminum',_'value':_'aluminum'}</t>
+          <t>aluminum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Aluminum', 'value': 'Aluminum'}</t>
+          <t>Aluminum</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'wood',_'value':_'wood'}</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Wood', 'value': 'Wood'}</t>
+          <t>Wood</t>
         </is>
       </c>
     </row>
